--- a/business_report_forms/006_impact_report_upload_form--business_report_forms.xlsx
+++ b/business_report_forms/006_impact_report_upload_form--business_report_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>first_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>First Page 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>first_page_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>First Page 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>first_page_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>First Page 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
